--- a/conf-data/excel/Datas/skill/skilleffect.xlsx
+++ b/conf-data/excel/Datas/skill/skilleffect.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\FY\FYGame\Data\excel\Datas\skill\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\opensrc\c++\gameSrv\conf-data\excel\Datas\skill\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{861C9C7F-0218-4A2D-A807-55BB0B5D5251}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2E04286-7927-4FC7-AEC5-1C477A9D5AED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7350" yWindow="3165" windowWidth="33210" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="index" sheetId="2" r:id="rId1"/>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="743" uniqueCount="582">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="745" uniqueCount="584">
   <si>
     <t>##var</t>
   </si>
@@ -2011,6 +2011,14 @@
   </si>
   <si>
     <t>净海子弹击中</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>alias</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>variants</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -2193,7 +2201,7 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2269,6 +2277,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="3" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -4338,7 +4349,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:N135"/>
+  <dimension ref="A1:P135"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="43.75" style="6" customWidth="1"/>
@@ -4347,16 +4358,16 @@
     <col min="4" max="5" width="9" style="6"/>
     <col min="6" max="6" width="9.125" style="6" customWidth="1"/>
     <col min="7" max="7" width="7.5" style="6" customWidth="1"/>
-    <col min="8" max="8" width="6.375" style="6" customWidth="1"/>
-    <col min="9" max="9" width="4" style="6" customWidth="1"/>
-    <col min="10" max="10" width="31.75" style="6" customWidth="1"/>
-    <col min="11" max="11" width="34.75" style="6" customWidth="1"/>
-    <col min="12" max="12" width="9" style="6"/>
-    <col min="13" max="13" width="76.5" style="6" customWidth="1"/>
-    <col min="14" max="16384" width="9" style="6"/>
+    <col min="8" max="10" width="16.375" style="6" customWidth="1"/>
+    <col min="11" max="11" width="18" style="6" customWidth="1"/>
+    <col min="12" max="12" width="31.75" style="6" customWidth="1"/>
+    <col min="13" max="13" width="34.75" style="6" customWidth="1"/>
+    <col min="14" max="14" width="9" style="6"/>
+    <col min="15" max="15" width="76.5" style="6" customWidth="1"/>
+    <col min="16" max="16384" width="9" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -4381,18 +4392,20 @@
       <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1"/>
+      <c r="J1"/>
+      <c r="K1" t="s">
         <v>9</v>
       </c>
-      <c r="J1" s="29" t="s">
+      <c r="L1" s="29" t="s">
         <v>289</v>
       </c>
-      <c r="K1" s="29"/>
-      <c r="L1" s="29"/>
       <c r="M1" s="29"/>
       <c r="N1" s="29"/>
-    </row>
-    <row r="2" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="O1" s="29"/>
+      <c r="P1" s="29"/>
+    </row>
+    <row r="2" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A2" s="8" t="s">
         <v>0</v>
       </c>
@@ -4403,24 +4416,30 @@
       <c r="F2" s="9"/>
       <c r="G2" s="9"/>
       <c r="H2" s="9"/>
-      <c r="I2" s="9"/>
-      <c r="J2" s="9" t="s">
+      <c r="I2" s="30" t="s">
+        <v>582</v>
+      </c>
+      <c r="J2" s="30" t="s">
+        <v>583</v>
+      </c>
+      <c r="K2" s="9"/>
+      <c r="L2" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="K2" s="9" t="s">
+      <c r="M2" s="9" t="s">
         <v>290</v>
       </c>
-      <c r="L2" s="9" t="s">
+      <c r="N2" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="M2" s="9" t="s">
+      <c r="O2" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="N2" s="9" t="s">
+      <c r="P2" s="9" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A3" s="10" t="s">
         <v>11</v>
       </c>
@@ -4436,21 +4455,23 @@
       <c r="G3" s="10"/>
       <c r="H3" s="10"/>
       <c r="I3" s="10"/>
-      <c r="J3" s="10" t="s">
+      <c r="J3" s="10"/>
+      <c r="K3" s="10"/>
+      <c r="L3" s="10" t="s">
         <v>292</v>
       </c>
-      <c r="K3" s="10" t="s">
+      <c r="M3" s="10" t="s">
         <v>293</v>
       </c>
-      <c r="L3" s="10" t="s">
+      <c r="N3" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="M3" s="10" t="s">
+      <c r="O3" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="N3" s="10"/>
-    </row>
-    <row r="4" spans="1:14" s="2" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="P3" s="10"/>
+    </row>
+    <row r="4" spans="1:16" s="2" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="10"/>
       <c r="B4" s="10"/>
       <c r="C4" s="10"/>
@@ -4465,32 +4486,34 @@
       <c r="L4" s="10"/>
       <c r="M4" s="10"/>
       <c r="N4" s="10"/>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="K5"/>
-      <c r="N5"/>
-    </row>
-    <row r="6" spans="1:14" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="O4" s="10"/>
+      <c r="P4" s="10"/>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.15">
+      <c r="M5"/>
+      <c r="P5"/>
+    </row>
+    <row r="6" spans="1:16" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A6" s="6"/>
       <c r="B6" s="6"/>
     </row>
-    <row r="7" spans="1:14" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:16" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A7" s="6"/>
       <c r="B7" s="6"/>
     </row>
-    <row r="8" spans="1:14" s="3" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A8" s="3" t="s">
         <v>294</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>295</v>
       </c>
-      <c r="N8" s="11"/>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="N9"/>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="P8" s="11"/>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.15">
+      <c r="P9"/>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A10" s="6" t="s">
         <v>296</v>
       </c>
@@ -4500,36 +4523,36 @@
       <c r="C10" s="22" t="s">
         <v>407</v>
       </c>
-      <c r="J10" s="6" t="s">
+      <c r="L10" s="6" t="s">
         <v>297</v>
       </c>
-      <c r="K10" s="6" t="s">
+      <c r="M10" s="6" t="s">
         <v>298</v>
       </c>
-      <c r="M10" s="6" t="s">
+      <c r="O10" s="6" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="J11" s="6" t="s">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.15">
+      <c r="L11" s="6" t="s">
         <v>300</v>
       </c>
-      <c r="K11" s="6" t="s">
+      <c r="M11" s="6" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="J12" s="6" t="s">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.15">
+      <c r="L12" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="K12" s="6" t="s">
+      <c r="M12" s="6" t="s">
         <v>301</v>
       </c>
-      <c r="M12" s="6" t="s">
+      <c r="O12" s="6" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A14" s="22" t="s">
         <v>504</v>
       </c>
@@ -4539,36 +4562,36 @@
       <c r="C14" s="6" t="s">
         <v>295</v>
       </c>
-      <c r="J14" s="6" t="s">
+      <c r="L14" s="6" t="s">
         <v>297</v>
       </c>
-      <c r="K14" s="22" t="s">
+      <c r="M14" s="22" t="s">
         <v>408</v>
       </c>
-      <c r="M14" s="6" t="s">
+      <c r="O14" s="6" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="J15" s="6" t="s">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.15">
+      <c r="L15" s="6" t="s">
         <v>300</v>
       </c>
-      <c r="K15" s="6" t="s">
+      <c r="M15" s="6" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="J16" s="6" t="s">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.15">
+      <c r="L16" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="K16" s="6" t="s">
+      <c r="M16" s="6" t="s">
         <v>301</v>
       </c>
-      <c r="M16" s="6" t="s">
+      <c r="O16" s="6" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A18" s="22" t="s">
         <v>505</v>
       </c>
@@ -4578,39 +4601,39 @@
       <c r="C18" s="6" t="s">
         <v>295</v>
       </c>
-      <c r="J18" s="22" t="s">
+      <c r="L18" s="22" t="s">
         <v>404</v>
       </c>
-      <c r="K18" s="22" t="s">
+      <c r="M18" s="22" t="s">
         <v>408</v>
       </c>
-      <c r="M18" s="6" t="s">
+      <c r="O18" s="6" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="J19" s="22" t="s">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="L19" s="22" t="s">
         <v>409</v>
       </c>
-      <c r="K19" s="6" t="s">
+      <c r="M19" s="6" t="s">
         <v>301</v>
       </c>
-      <c r="M19" s="22" t="s">
+      <c r="O19" s="22" t="s">
         <v>412</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="J20" s="22" t="s">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="L20" s="22" t="s">
         <v>410</v>
       </c>
-      <c r="K20" s="6" t="s">
+      <c r="M20" s="6" t="s">
         <v>301</v>
       </c>
-      <c r="M20" s="22" t="s">
+      <c r="O20" s="22" t="s">
         <v>411</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A22" s="22" t="s">
         <v>413</v>
       </c>
@@ -4620,21 +4643,21 @@
       <c r="C22" s="22" t="s">
         <v>415</v>
       </c>
-      <c r="J22" s="22" t="s">
+      <c r="L22" s="22" t="s">
         <v>417</v>
       </c>
-      <c r="K22" s="22" t="s">
+      <c r="M22" s="22" t="s">
         <v>418</v>
       </c>
-      <c r="M22" s="22" t="s">
+      <c r="O22" s="22" t="s">
         <v>416</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="J23" s="22"/>
-      <c r="M23" s="22"/>
-    </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="L23" s="22"/>
+      <c r="O23" s="22"/>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A24" s="6" t="s">
         <v>302</v>
       </c>
@@ -4645,31 +4668,31 @@
         <v>295</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="J25" s="6" t="s">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="L25" s="6" t="s">
         <v>304</v>
       </c>
-      <c r="K25" s="6" t="s">
+      <c r="M25" s="6" t="s">
         <v>305</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="J26" s="6" t="s">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="L26" s="6" t="s">
         <v>300</v>
       </c>
-      <c r="K26" s="6" t="s">
+      <c r="M26" s="6" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="J27" s="6" t="s">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="L27" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="K27" s="6" t="s">
+      <c r="M27" s="6" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A29" s="22" t="s">
         <v>427</v>
       </c>
@@ -4679,17 +4702,17 @@
       <c r="C29" s="6" t="s">
         <v>303</v>
       </c>
-      <c r="J29" s="6" t="s">
+      <c r="L29" s="6" t="s">
         <v>307</v>
       </c>
-      <c r="K29" s="6" t="s">
+      <c r="M29" s="6" t="s">
         <v>308</v>
       </c>
-      <c r="M29" s="6" t="s">
+      <c r="O29" s="6" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="30" spans="1:13" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A30" s="6"/>
       <c r="B30" s="6"/>
       <c r="C30" s="6"/>
@@ -4703,8 +4726,10 @@
       <c r="K30" s="6"/>
       <c r="L30" s="6"/>
       <c r="M30" s="6"/>
-    </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="N30" s="6"/>
+      <c r="O30" s="6"/>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A31" s="22" t="s">
         <v>426</v>
       </c>
@@ -4714,39 +4739,39 @@
       <c r="C31" s="6" t="s">
         <v>295</v>
       </c>
-      <c r="J31" s="22" t="s">
+      <c r="L31" s="22" t="s">
         <v>429</v>
       </c>
-      <c r="K31" s="22" t="s">
+      <c r="M31" s="22" t="s">
         <v>424</v>
       </c>
-      <c r="M31" s="22" t="s">
+      <c r="O31" s="22" t="s">
         <v>425</v>
       </c>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="J32" s="22" t="s">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="L32" s="22" t="s">
         <v>428</v>
       </c>
-      <c r="K32" s="22" t="s">
+      <c r="M32" s="22" t="s">
         <v>430</v>
       </c>
-      <c r="M32" s="23" t="s">
+      <c r="O32" s="23" t="s">
         <v>437</v>
       </c>
     </row>
-    <row r="33" spans="1:13" ht="27" x14ac:dyDescent="0.15">
-      <c r="J33" s="22" t="s">
+    <row r="33" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+      <c r="L33" s="22" t="s">
         <v>438</v>
       </c>
-      <c r="K33" s="22" t="s">
+      <c r="M33" s="22" t="s">
         <v>424</v>
       </c>
-      <c r="M33" s="23" t="s">
+      <c r="O33" s="23" t="s">
         <v>439</v>
       </c>
     </row>
-    <row r="34" spans="1:13" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A34" s="6"/>
       <c r="B34" s="6"/>
       <c r="C34" s="6"/>
@@ -4760,8 +4785,10 @@
       <c r="K34" s="6"/>
       <c r="L34" s="6"/>
       <c r="M34" s="6"/>
-    </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="N34" s="6"/>
+      <c r="O34" s="6"/>
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A35" s="6" t="s">
         <v>310</v>
       </c>
@@ -4771,17 +4798,17 @@
       <c r="C35" s="6" t="s">
         <v>303</v>
       </c>
-      <c r="J35" s="6" t="s">
+      <c r="L35" s="6" t="s">
         <v>312</v>
       </c>
-      <c r="K35" s="6" t="s">
+      <c r="M35" s="6" t="s">
         <v>313</v>
       </c>
-      <c r="M35" t="s">
+      <c r="O35" t="s">
         <v>314</v>
       </c>
     </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A37" s="6" t="s">
         <v>315</v>
       </c>
@@ -4791,25 +4818,25 @@
       <c r="C37" s="6" t="s">
         <v>295</v>
       </c>
-      <c r="J37" s="6" t="s">
+      <c r="L37" s="6" t="s">
         <v>317</v>
       </c>
-      <c r="K37" s="6" t="s">
+      <c r="M37" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="M37" s="6" t="s">
+      <c r="O37" s="6" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="J38" s="6" t="s">
+    <row r="38" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="L38" s="6" t="s">
         <v>318</v>
       </c>
-      <c r="K38" s="6" t="s">
+      <c r="M38" s="6" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A40" s="6" t="s">
         <v>319</v>
       </c>
@@ -4819,28 +4846,28 @@
       <c r="C40" s="6" t="s">
         <v>295</v>
       </c>
-      <c r="J40" s="6" t="s">
+      <c r="L40" s="6" t="s">
         <v>321</v>
       </c>
-      <c r="K40" s="6" t="s">
+      <c r="M40" s="6" t="s">
         <v>308</v>
       </c>
-      <c r="M40" s="6" t="s">
+      <c r="O40" s="6" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="J41" s="22" t="s">
+    <row r="41" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="L41" s="22" t="s">
         <v>488</v>
       </c>
-      <c r="K41" s="22" t="s">
+      <c r="M41" s="22" t="s">
         <v>489</v>
       </c>
-      <c r="M41" s="22" t="s">
+      <c r="O41" s="22" t="s">
         <v>490</v>
       </c>
     </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A43" s="6" t="s">
         <v>323</v>
       </c>
@@ -4850,28 +4877,28 @@
       <c r="C43" s="6" t="s">
         <v>295</v>
       </c>
-      <c r="J43" s="6" t="s">
+      <c r="L43" s="6" t="s">
         <v>325</v>
       </c>
-      <c r="K43" s="6" t="s">
+      <c r="M43" s="6" t="s">
         <v>250</v>
       </c>
-      <c r="M43" s="6" t="s">
+      <c r="O43" s="6" t="s">
         <v>326</v>
       </c>
     </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="J44" s="6" t="s">
+    <row r="44" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="L44" s="6" t="s">
         <v>327</v>
       </c>
-      <c r="K44" s="6" t="s">
+      <c r="M44" s="6" t="s">
         <v>308</v>
       </c>
-      <c r="M44" s="6" t="s">
+      <c r="O44" s="6" t="s">
         <v>328</v>
       </c>
     </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A46" s="6" t="s">
         <v>329</v>
       </c>
@@ -4881,20 +4908,20 @@
       <c r="C46" s="6" t="s">
         <v>295</v>
       </c>
-      <c r="J46" s="18" t="s">
+      <c r="L46" s="18" t="s">
         <v>540</v>
       </c>
-      <c r="K46" s="22" t="s">
+      <c r="M46" s="22" t="s">
         <v>539</v>
       </c>
-      <c r="M46" s="22" t="s">
+      <c r="O46" s="22" t="s">
         <v>541</v>
       </c>
     </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="J47"/>
-    </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="L47"/>
+    </row>
+    <row r="48" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A48" s="6" t="s">
         <v>332</v>
       </c>
@@ -4904,28 +4931,28 @@
       <c r="C48" s="6" t="s">
         <v>295</v>
       </c>
-      <c r="J48" s="18" t="s">
+      <c r="L48" s="18" t="s">
         <v>465</v>
       </c>
-      <c r="K48" s="6" t="s">
+      <c r="M48" s="6" t="s">
         <v>301</v>
       </c>
-      <c r="M48" s="6" t="s">
+      <c r="O48" s="6" t="s">
         <v>334</v>
       </c>
     </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="J49" s="6" t="s">
+    <row r="49" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="L49" s="6" t="s">
         <v>335</v>
       </c>
-      <c r="K49" s="6" t="s">
+      <c r="M49" s="6" t="s">
         <v>336</v>
       </c>
-      <c r="M49" s="6" t="s">
+      <c r="O49" s="6" t="s">
         <v>337</v>
       </c>
     </row>
-    <row r="51" spans="1:13" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A51" s="6" t="s">
         <v>338</v>
       </c>
@@ -4935,24 +4962,24 @@
       <c r="C51" s="6" t="s">
         <v>295</v>
       </c>
-      <c r="J51" s="6" t="s">
+      <c r="L51" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="K51" s="6" t="s">
+      <c r="M51" s="6" t="s">
         <v>340</v>
       </c>
-      <c r="M51" s="6" t="s">
+      <c r="O51" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="52" spans="1:13" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A52" s="6"/>
       <c r="B52" s="6"/>
-      <c r="J52" s="6"/>
-      <c r="K52" s="6"/>
+      <c r="L52" s="6"/>
       <c r="M52" s="6"/>
-    </row>
-    <row r="53" spans="1:13" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="O52" s="6"/>
+    </row>
+    <row r="53" spans="1:15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A53" s="6" t="s">
         <v>341</v>
       </c>
@@ -4962,24 +4989,24 @@
       <c r="C53" s="6" t="s">
         <v>295</v>
       </c>
-      <c r="J53" s="6" t="s">
+      <c r="L53" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="K53" s="22" t="s">
+      <c r="M53" s="22" t="s">
         <v>467</v>
       </c>
-      <c r="M53" s="6" t="s">
+      <c r="O53" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="54" spans="1:13" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A54" s="6"/>
       <c r="B54" s="6"/>
-      <c r="J54" s="6"/>
-      <c r="K54" s="6"/>
+      <c r="L54" s="6"/>
       <c r="M54" s="6"/>
-    </row>
-    <row r="55" spans="1:13" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="O54" s="6"/>
+    </row>
+    <row r="55" spans="1:15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A55" s="22" t="s">
         <v>463</v>
       </c>
@@ -4989,24 +5016,24 @@
       <c r="C55" s="6" t="s">
         <v>295</v>
       </c>
-      <c r="J55" s="22" t="s">
+      <c r="L55" s="22" t="s">
         <v>466</v>
       </c>
-      <c r="K55" s="22" t="s">
+      <c r="M55" s="22" t="s">
         <v>468</v>
       </c>
-      <c r="M55" s="22" t="s">
+      <c r="O55" s="22" t="s">
         <v>469</v>
       </c>
     </row>
-    <row r="56" spans="1:13" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A56" s="6"/>
       <c r="B56" s="6"/>
-      <c r="J56" s="6"/>
-      <c r="K56" s="6"/>
+      <c r="L56" s="6"/>
       <c r="M56" s="6"/>
-    </row>
-    <row r="57" spans="1:13" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="O56" s="6"/>
+    </row>
+    <row r="57" spans="1:15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A57" s="22" t="s">
         <v>473</v>
       </c>
@@ -5016,108 +5043,108 @@
       <c r="C57" s="6" t="s">
         <v>295</v>
       </c>
-      <c r="J57" s="22" t="s">
+      <c r="L57" s="22" t="s">
         <v>475</v>
       </c>
-      <c r="K57" s="22" t="s">
+      <c r="M57" s="22" t="s">
         <v>408</v>
       </c>
-      <c r="M57" s="22" t="s">
+      <c r="O57" s="22" t="s">
         <v>476</v>
       </c>
     </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="J58" s="22" t="s">
+    <row r="58" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="L58" s="22" t="s">
         <v>485</v>
       </c>
-      <c r="K58" s="22" t="s">
+      <c r="M58" s="22" t="s">
         <v>477</v>
       </c>
-      <c r="M58" s="22" t="s">
+      <c r="O58" s="22" t="s">
         <v>478</v>
       </c>
     </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="J59" s="22" t="s">
+    <row r="59" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="L59" s="22" t="s">
         <v>484</v>
       </c>
-      <c r="K59" s="22" t="s">
+      <c r="M59" s="22" t="s">
         <v>408</v>
       </c>
-      <c r="M59" s="22" t="s">
+      <c r="O59" s="22" t="s">
         <v>479</v>
       </c>
     </row>
-    <row r="60" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="J60" s="22" t="s">
+    <row r="60" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="L60" s="22" t="s">
         <v>482</v>
       </c>
-      <c r="K60" s="22" t="s">
+      <c r="M60" s="22" t="s">
         <v>424</v>
       </c>
-      <c r="M60" s="22" t="s">
+      <c r="O60" s="22" t="s">
         <v>483</v>
       </c>
     </row>
-    <row r="61" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="J61" s="22" t="s">
+    <row r="61" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="L61" s="22" t="s">
         <v>480</v>
       </c>
-      <c r="K61" s="22" t="s">
+      <c r="M61" s="22" t="s">
         <v>424</v>
       </c>
-      <c r="M61" s="22" t="s">
+      <c r="O61" s="22" t="s">
         <v>481</v>
       </c>
     </row>
-    <row r="62" spans="1:13" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A62" s="6"/>
       <c r="B62" s="6"/>
-      <c r="J62" s="6"/>
-      <c r="K62" s="6"/>
+      <c r="L62" s="6"/>
       <c r="M62" s="6"/>
-    </row>
-    <row r="63" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="O62" s="6"/>
+    </row>
+    <row r="63" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A63" s="4" t="s">
         <v>343</v>
       </c>
       <c r="B63" s="4" t="s">
         <v>344</v>
       </c>
-      <c r="J63" s="4" t="s">
+      <c r="L63" s="4" t="s">
         <v>345</v>
       </c>
-      <c r="K63" s="12" t="s">
+      <c r="M63" s="12" t="s">
         <v>101</v>
       </c>
-      <c r="M63" s="4" t="s">
+      <c r="O63" s="4" t="s">
         <v>346</v>
       </c>
     </row>
-    <row r="64" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A64" s="4"/>
-      <c r="J64" s="6" t="s">
+      <c r="L64" s="6" t="s">
         <v>347</v>
       </c>
-      <c r="K64" s="6" t="s">
+      <c r="M64" s="6" t="s">
         <v>308</v>
       </c>
-      <c r="M64" s="6" t="s">
+      <c r="O64" s="6" t="s">
         <v>348</v>
       </c>
     </row>
-    <row r="65" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="J65" s="6" t="s">
+    <row r="65" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="L65" s="6" t="s">
         <v>349</v>
       </c>
-      <c r="K65" s="6" t="s">
+      <c r="M65" s="6" t="s">
         <v>308</v>
       </c>
-      <c r="M65" s="6" t="s">
+      <c r="O65" s="6" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="67" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A67" s="6" t="s">
         <v>351</v>
       </c>
@@ -5127,14 +5154,14 @@
       <c r="C67" s="6" t="s">
         <v>344</v>
       </c>
-      <c r="J67" s="6" t="s">
+      <c r="L67" s="6" t="s">
         <v>353</v>
       </c>
-      <c r="K67" s="6" t="s">
+      <c r="M67" s="6" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="69" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A69" s="6" t="s">
         <v>355</v>
       </c>
@@ -5144,17 +5171,17 @@
       <c r="C69" s="6" t="s">
         <v>344</v>
       </c>
-      <c r="J69" s="6" t="s">
+      <c r="L69" s="6" t="s">
         <v>357</v>
       </c>
-      <c r="K69" s="6" t="s">
+      <c r="M69" s="6" t="s">
         <v>301</v>
       </c>
-      <c r="M69" s="6" t="s">
+      <c r="O69" s="6" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="72" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A72" s="6" t="s">
         <v>358</v>
       </c>
@@ -5164,24 +5191,24 @@
       <c r="C72" s="6" t="s">
         <v>344</v>
       </c>
-      <c r="J72" s="6" t="s">
+      <c r="L72" s="6" t="s">
         <v>360</v>
       </c>
-      <c r="K72" s="6" t="s">
+      <c r="M72" s="6" t="s">
         <v>354</v>
       </c>
-      <c r="M72" s="6" t="s">
+      <c r="O72" s="6" t="s">
         <v>361</v>
       </c>
     </row>
-    <row r="74" spans="1:13" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A74" s="6"/>
       <c r="B74" s="6"/>
-      <c r="J74" s="6"/>
-      <c r="K74" s="6"/>
+      <c r="L74" s="6"/>
       <c r="M74" s="6"/>
-    </row>
-    <row r="75" spans="1:13" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="O74" s="6"/>
+    </row>
+    <row r="75" spans="1:15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A75" s="22" t="s">
         <v>500</v>
       </c>
@@ -5191,50 +5218,50 @@
       <c r="C75" s="6" t="s">
         <v>344</v>
       </c>
-      <c r="J75" s="6" t="s">
+      <c r="L75" s="6" t="s">
         <v>363</v>
       </c>
-      <c r="K75" s="6" t="s">
+      <c r="M75" s="6" t="s">
         <v>298</v>
       </c>
-      <c r="M75" s="6" t="s">
+      <c r="O75" s="6" t="s">
         <v>364</v>
       </c>
     </row>
-    <row r="76" spans="1:13" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A76" s="6"/>
       <c r="B76" s="6"/>
-      <c r="J76" s="6" t="s">
+      <c r="L76" s="6" t="s">
         <v>365</v>
       </c>
-      <c r="K76" s="6" t="s">
+      <c r="M76" s="6" t="s">
         <v>211</v>
       </c>
-      <c r="M76" s="6" t="s">
+      <c r="O76" s="6" t="s">
         <v>366</v>
       </c>
     </row>
-    <row r="77" spans="1:13" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A77" s="6"/>
       <c r="B77" s="6"/>
-      <c r="J77" s="6" t="s">
+      <c r="L77" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="K77" s="6" t="s">
+      <c r="M77" s="6" t="s">
         <v>301</v>
       </c>
-      <c r="M77" s="6" t="s">
+      <c r="O77" s="6" t="s">
         <v>367</v>
       </c>
     </row>
-    <row r="78" spans="1:13" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A78" s="6"/>
       <c r="B78" s="6"/>
-      <c r="J78" s="6"/>
-      <c r="K78" s="6"/>
+      <c r="L78" s="6"/>
       <c r="M78" s="6"/>
-    </row>
-    <row r="79" spans="1:13" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="O78" s="6"/>
+    </row>
+    <row r="79" spans="1:15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A79" s="6" t="s">
         <v>368</v>
       </c>
@@ -5244,36 +5271,36 @@
       <c r="C79" s="6" t="s">
         <v>344</v>
       </c>
-      <c r="J79" s="6" t="s">
+      <c r="L79" s="6" t="s">
         <v>317</v>
       </c>
-      <c r="K79" s="6" t="s">
+      <c r="M79" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="M79" s="6" t="s">
+      <c r="O79" s="6" t="s">
         <v>370</v>
       </c>
     </row>
-    <row r="80" spans="1:13" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A80" s="6"/>
       <c r="B80" s="6"/>
       <c r="C80" s="6"/>
-      <c r="J80" s="6" t="s">
+      <c r="L80" s="6" t="s">
         <v>371</v>
       </c>
-      <c r="K80" s="6" t="s">
+      <c r="M80" s="6" t="s">
         <v>301</v>
       </c>
-      <c r="M80" s="6"/>
-    </row>
-    <row r="81" spans="1:13" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="O80" s="6"/>
+    </row>
+    <row r="81" spans="1:15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A81" s="6"/>
       <c r="B81" s="6"/>
-      <c r="J81" s="6"/>
-      <c r="K81" s="6"/>
+      <c r="L81" s="6"/>
       <c r="M81" s="6"/>
-    </row>
-    <row r="82" spans="1:13" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="O81" s="6"/>
+    </row>
+    <row r="82" spans="1:15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A82" s="6" t="s">
         <v>372</v>
       </c>
@@ -5283,25 +5310,25 @@
       <c r="C82" s="6" t="s">
         <v>344</v>
       </c>
-      <c r="J82" s="6" t="s">
+      <c r="L82" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="K82" s="22" t="s">
+      <c r="M82" s="22" t="s">
         <v>452</v>
       </c>
-      <c r="M82" s="6" t="s">
+      <c r="O82" s="6" t="s">
         <v>374</v>
       </c>
     </row>
-    <row r="83" spans="1:13" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="83" spans="1:15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A83" s="6"/>
       <c r="B83" s="6"/>
       <c r="C83" s="6"/>
-      <c r="J83" s="6"/>
-      <c r="K83" s="6"/>
+      <c r="L83" s="6"/>
       <c r="M83" s="6"/>
-    </row>
-    <row r="84" spans="1:13" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="O83" s="6"/>
+    </row>
+    <row r="84" spans="1:15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A84" s="22" t="s">
         <v>492</v>
       </c>
@@ -5311,25 +5338,25 @@
       <c r="C84" s="6" t="s">
         <v>344</v>
       </c>
-      <c r="J84" s="22" t="s">
+      <c r="L84" s="22" t="s">
         <v>494</v>
       </c>
-      <c r="K84" s="22" t="s">
+      <c r="M84" s="22" t="s">
         <v>493</v>
       </c>
-      <c r="M84" s="22" t="s">
+      <c r="O84" s="22" t="s">
         <v>495</v>
       </c>
     </row>
-    <row r="85" spans="1:13" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A85" s="6"/>
       <c r="B85" s="6"/>
       <c r="C85" s="6"/>
-      <c r="J85" s="6"/>
-      <c r="K85" s="6"/>
+      <c r="L85" s="6"/>
       <c r="M85" s="6"/>
-    </row>
-    <row r="86" spans="1:13" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="O85" s="6"/>
+    </row>
+    <row r="86" spans="1:15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A86" s="22" t="s">
         <v>576</v>
       </c>
@@ -5339,25 +5366,25 @@
       <c r="C86" s="6" t="s">
         <v>344</v>
       </c>
-      <c r="J86" s="6" t="s">
+      <c r="L86" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="K86" s="6" t="s">
+      <c r="M86" s="6" t="s">
         <v>308</v>
       </c>
-      <c r="M86" s="6" t="s">
+      <c r="O86" s="6" t="s">
         <v>374</v>
       </c>
     </row>
-    <row r="87" spans="1:13" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A87" s="6"/>
       <c r="B87" s="6"/>
       <c r="C87" s="6"/>
-      <c r="J87" s="6"/>
-      <c r="K87" s="6"/>
+      <c r="L87" s="6"/>
       <c r="M87" s="6"/>
-    </row>
-    <row r="88" spans="1:13" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="O87" s="6"/>
+    </row>
+    <row r="88" spans="1:15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A88" s="6" t="s">
         <v>376</v>
       </c>
@@ -5367,24 +5394,24 @@
       <c r="C88" s="6" t="s">
         <v>344</v>
       </c>
-      <c r="J88" s="6" t="s">
+      <c r="L88" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="K88" s="6" t="s">
+      <c r="M88" s="6" t="s">
         <v>308</v>
       </c>
-      <c r="M88" s="6" t="s">
+      <c r="O88" s="6" t="s">
         <v>374</v>
       </c>
     </row>
-    <row r="89" spans="1:13" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="89" spans="1:15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A89" s="6"/>
       <c r="B89" s="6"/>
-      <c r="J89" s="6"/>
-      <c r="K89" s="6"/>
+      <c r="L89" s="6"/>
       <c r="M89" s="6"/>
-    </row>
-    <row r="90" spans="1:13" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="O89" s="6"/>
+    </row>
+    <row r="90" spans="1:15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A90" s="6" t="s">
         <v>121</v>
       </c>
@@ -5394,24 +5421,24 @@
       <c r="C90" s="6" t="s">
         <v>344</v>
       </c>
-      <c r="J90" s="6" t="s">
+      <c r="L90" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="K90" s="6" t="s">
+      <c r="M90" s="6" t="s">
         <v>308</v>
       </c>
-      <c r="M90" s="6" t="s">
+      <c r="O90" s="6" t="s">
         <v>374</v>
       </c>
     </row>
-    <row r="91" spans="1:13" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="91" spans="1:15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A91" s="6"/>
       <c r="B91" s="6"/>
-      <c r="J91" s="6"/>
-      <c r="K91" s="6"/>
+      <c r="L91" s="6"/>
       <c r="M91" s="6"/>
-    </row>
-    <row r="92" spans="1:13" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="O91" s="6"/>
+    </row>
+    <row r="92" spans="1:15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A92" s="22" t="s">
         <v>577</v>
       </c>
@@ -5421,31 +5448,31 @@
       <c r="C92" s="6" t="s">
         <v>344</v>
       </c>
-      <c r="J92" s="6" t="s">
+      <c r="L92" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="K92" s="6" t="s">
+      <c r="M92" s="6" t="s">
         <v>308</v>
       </c>
-      <c r="M92" s="6" t="s">
+      <c r="O92" s="6" t="s">
         <v>374</v>
       </c>
     </row>
-    <row r="93" spans="1:13" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="93" spans="1:15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A93" s="6"/>
       <c r="B93" s="6"/>
-      <c r="J93" s="6"/>
-      <c r="K93" s="6"/>
+      <c r="L93" s="6"/>
       <c r="M93" s="6"/>
-    </row>
-    <row r="94" spans="1:13" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="O93" s="6"/>
+    </row>
+    <row r="94" spans="1:15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A94" s="6"/>
       <c r="B94" s="6"/>
-      <c r="J94" s="6"/>
-      <c r="K94" s="6"/>
+      <c r="L94" s="6"/>
       <c r="M94" s="6"/>
-    </row>
-    <row r="95" spans="1:13" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="O94" s="6"/>
+    </row>
+    <row r="95" spans="1:15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A95" s="6" t="s">
         <v>380</v>
       </c>
@@ -5455,31 +5482,31 @@
       <c r="C95" s="6" t="s">
         <v>344</v>
       </c>
-      <c r="J95" s="6" t="s">
+      <c r="L95" s="6" t="s">
         <v>382</v>
       </c>
-      <c r="K95" s="6" t="s">
+      <c r="M95" s="6" t="s">
         <v>301</v>
       </c>
-      <c r="M95" s="6" t="s">
+      <c r="O95" s="6" t="s">
         <v>383</v>
       </c>
     </row>
-    <row r="96" spans="1:13" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="96" spans="1:15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A96" s="6"/>
       <c r="B96" s="6"/>
-      <c r="J96" s="6"/>
-      <c r="K96" s="6"/>
+      <c r="L96" s="6"/>
       <c r="M96" s="6"/>
-    </row>
-    <row r="97" spans="1:13" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="O96" s="6"/>
+    </row>
+    <row r="97" spans="1:15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A97" s="6"/>
       <c r="B97" s="6"/>
-      <c r="J97" s="6"/>
-      <c r="K97" s="6"/>
+      <c r="L97" s="6"/>
       <c r="M97" s="6"/>
-    </row>
-    <row r="98" spans="1:13" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="O97" s="6"/>
+    </row>
+    <row r="98" spans="1:15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A98" s="6" t="s">
         <v>384</v>
       </c>
@@ -5489,25 +5516,25 @@
       <c r="C98" s="6" t="s">
         <v>344</v>
       </c>
-      <c r="J98" s="6" t="s">
+      <c r="L98" s="6" t="s">
         <v>386</v>
       </c>
-      <c r="K98" s="6" t="s">
+      <c r="M98" s="6" t="s">
         <v>308</v>
       </c>
-      <c r="M98" s="6" t="s">
+      <c r="O98" s="6" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="99" spans="1:13" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="99" spans="1:15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A99" s="6"/>
       <c r="B99" s="6"/>
       <c r="C99" s="6"/>
-      <c r="J99" s="6"/>
-      <c r="K99" s="6"/>
+      <c r="L99" s="6"/>
       <c r="M99" s="6"/>
-    </row>
-    <row r="100" spans="1:13" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="O99" s="6"/>
+    </row>
+    <row r="100" spans="1:15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A100" s="22" t="s">
         <v>531</v>
       </c>
@@ -5517,25 +5544,25 @@
       <c r="C100" s="6" t="s">
         <v>344</v>
       </c>
-      <c r="J100" s="22" t="s">
+      <c r="L100" s="22" t="s">
         <v>530</v>
       </c>
-      <c r="K100" s="22" t="s">
+      <c r="M100" s="22" t="s">
         <v>551</v>
       </c>
-      <c r="M100" s="6" t="s">
+      <c r="O100" s="6" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="101" spans="1:13" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="101" spans="1:15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A101" s="6"/>
       <c r="B101" s="6"/>
       <c r="C101" s="6"/>
-      <c r="J101" s="6"/>
-      <c r="K101" s="6"/>
+      <c r="L101" s="6"/>
       <c r="M101" s="6"/>
-    </row>
-    <row r="102" spans="1:13" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="O101" s="6"/>
+    </row>
+    <row r="102" spans="1:15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A102" s="6" t="s">
         <v>388</v>
       </c>
@@ -5545,25 +5572,25 @@
       <c r="C102" s="6" t="s">
         <v>344</v>
       </c>
-      <c r="J102" s="6" t="s">
+      <c r="L102" s="6" t="s">
         <v>312</v>
       </c>
-      <c r="K102" s="6" t="s">
+      <c r="M102" s="6" t="s">
         <v>389</v>
       </c>
-      <c r="M102" s="6" t="s">
+      <c r="O102" s="6" t="s">
         <v>390</v>
       </c>
     </row>
-    <row r="103" spans="1:13" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="103" spans="1:15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A103" s="6"/>
       <c r="B103" s="6"/>
       <c r="C103" s="6"/>
-      <c r="J103" s="6"/>
-      <c r="K103" s="6"/>
+      <c r="L103" s="6"/>
       <c r="M103" s="6"/>
-    </row>
-    <row r="104" spans="1:13" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="O103" s="6"/>
+    </row>
+    <row r="104" spans="1:15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A104" s="22" t="s">
         <v>513</v>
       </c>
@@ -5573,25 +5600,25 @@
       <c r="C104" s="22" t="s">
         <v>515</v>
       </c>
-      <c r="J104" s="22" t="s">
+      <c r="L104" s="22" t="s">
         <v>518</v>
       </c>
-      <c r="K104" s="22" t="s">
+      <c r="M104" s="22" t="s">
         <v>516</v>
       </c>
-      <c r="M104" s="22" t="s">
+      <c r="O104" s="22" t="s">
         <v>517</v>
       </c>
     </row>
-    <row r="105" spans="1:13" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="105" spans="1:15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A105" s="6"/>
       <c r="B105" s="6"/>
       <c r="C105" s="6"/>
-      <c r="J105" s="6"/>
-      <c r="K105" s="6"/>
+      <c r="L105" s="6"/>
       <c r="M105" s="6"/>
-    </row>
-    <row r="106" spans="1:13" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="O105" s="6"/>
+    </row>
+    <row r="106" spans="1:15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A106" s="22" t="s">
         <v>521</v>
       </c>
@@ -5601,39 +5628,39 @@
       <c r="C106" s="22" t="s">
         <v>515</v>
       </c>
-      <c r="J106" s="22" t="s">
+      <c r="L106" s="22" t="s">
         <v>518</v>
       </c>
-      <c r="K106" s="22" t="s">
+      <c r="M106" s="22" t="s">
         <v>516</v>
       </c>
-      <c r="M106" s="22" t="s">
+      <c r="O106" s="22" t="s">
         <v>517</v>
       </c>
     </row>
-    <row r="107" spans="1:13" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="107" spans="1:15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A107" s="6"/>
       <c r="B107" s="6"/>
       <c r="C107" s="6"/>
-      <c r="J107" s="22" t="s">
+      <c r="L107" s="22" t="s">
         <v>523</v>
       </c>
-      <c r="K107" s="6" t="s">
+      <c r="M107" s="6" t="s">
         <v>301</v>
       </c>
-      <c r="M107" s="22" t="s">
+      <c r="O107" s="22" t="s">
         <v>524</v>
       </c>
     </row>
-    <row r="108" spans="1:13" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="108" spans="1:15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A108" s="6"/>
       <c r="B108" s="6"/>
       <c r="C108" s="6"/>
-      <c r="J108" s="6"/>
-      <c r="K108" s="6"/>
+      <c r="L108" s="6"/>
       <c r="M108" s="6"/>
-    </row>
-    <row r="109" spans="1:13" s="26" customFormat="1" ht="40.5" x14ac:dyDescent="0.15">
+      <c r="O108" s="6"/>
+    </row>
+    <row r="109" spans="1:15" s="26" customFormat="1" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A109" s="25" t="s">
         <v>544</v>
       </c>
@@ -5643,25 +5670,25 @@
       <c r="C109" s="25" t="s">
         <v>515</v>
       </c>
-      <c r="J109" s="25" t="s">
+      <c r="L109" s="25" t="s">
         <v>542</v>
       </c>
-      <c r="K109" s="25" t="s">
+      <c r="M109" s="25" t="s">
         <v>424</v>
       </c>
-      <c r="M109" s="27" t="s">
+      <c r="O109" s="27" t="s">
         <v>543</v>
       </c>
     </row>
-    <row r="110" spans="1:13" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="110" spans="1:15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A110" s="6"/>
       <c r="B110" s="6"/>
       <c r="C110" s="6"/>
-      <c r="J110" s="6"/>
-      <c r="K110" s="6"/>
+      <c r="L110" s="6"/>
       <c r="M110" s="6"/>
-    </row>
-    <row r="111" spans="1:13" s="26" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="O110" s="6"/>
+    </row>
+    <row r="111" spans="1:15" s="26" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A111" s="25" t="s">
         <v>546</v>
       </c>
@@ -5671,39 +5698,39 @@
       <c r="C111" s="25" t="s">
         <v>515</v>
       </c>
-      <c r="J111" s="25" t="s">
+      <c r="L111" s="25" t="s">
         <v>548</v>
       </c>
-      <c r="K111" s="25" t="s">
+      <c r="M111" s="25" t="s">
         <v>408</v>
       </c>
-      <c r="M111" s="27" t="s">
+      <c r="O111" s="27" t="s">
         <v>549</v>
       </c>
     </row>
-    <row r="112" spans="1:13" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="112" spans="1:15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A112" s="6"/>
       <c r="B112" s="6"/>
       <c r="C112" s="6"/>
-      <c r="J112" s="22" t="s">
+      <c r="L112" s="22" t="s">
         <v>552</v>
       </c>
-      <c r="K112" s="22" t="s">
+      <c r="M112" s="22" t="s">
         <v>442</v>
       </c>
-      <c r="M112" s="6" t="s">
+      <c r="O112" s="6" t="s">
         <v>550</v>
       </c>
     </row>
-    <row r="113" spans="1:13" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="113" spans="1:15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A113" s="6"/>
       <c r="B113" s="6"/>
       <c r="C113" s="6"/>
-      <c r="J113" s="6"/>
-      <c r="K113" s="6"/>
+      <c r="L113" s="6"/>
       <c r="M113" s="6"/>
-    </row>
-    <row r="114" spans="1:13" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="O113" s="6"/>
+    </row>
+    <row r="114" spans="1:15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A114" s="22" t="s">
         <v>537</v>
       </c>
@@ -5713,28 +5740,28 @@
       <c r="C114" s="22" t="s">
         <v>515</v>
       </c>
-      <c r="J114" s="6"/>
-      <c r="K114" s="6"/>
+      <c r="L114" s="6"/>
       <c r="M114" s="6"/>
-    </row>
-    <row r="115" spans="1:13" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="O114" s="6"/>
+    </row>
+    <row r="115" spans="1:15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A115" s="6"/>
       <c r="B115" s="6"/>
       <c r="C115" s="6"/>
-      <c r="J115" s="6"/>
-      <c r="K115" s="6"/>
+      <c r="L115" s="6"/>
       <c r="M115" s="6"/>
-    </row>
-    <row r="116" spans="1:13" s="5" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="O115" s="6"/>
+    </row>
+    <row r="116" spans="1:15" s="5" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A116" s="5" t="s">
         <v>391</v>
       </c>
       <c r="B116" s="5" t="s">
         <v>392</v>
       </c>
-      <c r="K116" s="13"/>
-    </row>
-    <row r="120" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="M116" s="13"/>
+    </row>
+    <row r="120" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A120" s="6" t="s">
         <v>393</v>
       </c>
@@ -5744,14 +5771,14 @@
       <c r="C120" s="6" t="s">
         <v>392</v>
       </c>
-      <c r="J120" s="6" t="s">
+      <c r="L120" s="6" t="s">
         <v>395</v>
       </c>
-      <c r="K120" s="6" t="s">
+      <c r="M120" s="6" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="122" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="122" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A122" s="6" t="s">
         <v>396</v>
       </c>
@@ -5761,14 +5788,14 @@
       <c r="C122" s="6" t="s">
         <v>392</v>
       </c>
-      <c r="J122" s="6" t="s">
+      <c r="L122" s="6" t="s">
         <v>395</v>
       </c>
-      <c r="K122" s="6" t="s">
+      <c r="M122" s="6" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="124" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="124" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A124" s="6" t="s">
         <v>398</v>
       </c>
@@ -5778,14 +5805,14 @@
       <c r="C124" s="6" t="s">
         <v>392</v>
       </c>
-      <c r="J124" s="6" t="s">
+      <c r="L124" s="6" t="s">
         <v>400</v>
       </c>
-      <c r="K124" s="6" t="s">
+      <c r="M124" s="6" t="s">
         <v>308</v>
       </c>
     </row>
-    <row r="126" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="126" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A126" s="22" t="s">
         <v>525</v>
       </c>
@@ -5795,17 +5822,17 @@
       <c r="C126" s="6" t="s">
         <v>392</v>
       </c>
-      <c r="J126" s="22" t="s">
+      <c r="L126" s="22" t="s">
         <v>526</v>
       </c>
-      <c r="K126" s="22" t="s">
+      <c r="M126" s="22" t="s">
         <v>529</v>
       </c>
-      <c r="M126" s="22" t="s">
+      <c r="O126" s="22" t="s">
         <v>527</v>
       </c>
     </row>
-    <row r="128" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="128" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A128" s="22" t="s">
         <v>444</v>
       </c>
@@ -5815,14 +5842,14 @@
       <c r="C128" s="22" t="s">
         <v>441</v>
       </c>
-      <c r="J128" s="22" t="s">
+      <c r="L128" s="22" t="s">
         <v>443</v>
       </c>
-      <c r="K128" s="22" t="s">
+      <c r="M128" s="22" t="s">
         <v>442</v>
       </c>
     </row>
-    <row r="130" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="130" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A130" s="22" t="s">
         <v>458</v>
       </c>
@@ -5832,14 +5859,14 @@
       <c r="C130" s="22" t="s">
         <v>441</v>
       </c>
-      <c r="J130" s="22" t="s">
+      <c r="L130" s="22" t="s">
         <v>456</v>
       </c>
-      <c r="K130" s="22" t="s">
+      <c r="M130" s="22" t="s">
         <v>462</v>
       </c>
     </row>
-    <row r="132" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="132" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A132" s="22" t="s">
         <v>459</v>
       </c>
@@ -5849,14 +5876,14 @@
       <c r="C132" s="22" t="s">
         <v>441</v>
       </c>
-      <c r="J132" s="22" t="s">
+      <c r="L132" s="22" t="s">
         <v>460</v>
       </c>
-      <c r="K132" s="22" t="s">
+      <c r="M132" s="22" t="s">
         <v>461</v>
       </c>
     </row>
-    <row r="134" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="134" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A134" s="22" t="s">
         <v>470</v>
       </c>
@@ -5866,27 +5893,27 @@
       <c r="C134" s="22" t="s">
         <v>441</v>
       </c>
-      <c r="J134" s="22" t="s">
+      <c r="L134" s="22" t="s">
         <v>472</v>
       </c>
-      <c r="K134" s="22" t="s">
+      <c r="M134" s="22" t="s">
         <v>442</v>
       </c>
     </row>
-    <row r="135" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="J135" s="22" t="s">
+    <row r="135" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="L135" s="22" t="s">
         <v>486</v>
       </c>
-      <c r="K135" s="22" t="s">
+      <c r="M135" s="22" t="s">
         <v>424</v>
       </c>
-      <c r="M135" s="22" t="s">
+      <c r="O135" s="22" t="s">
         <v>487</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="J1:N1"/>
+    <mergeCell ref="L1:P1"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
